--- a/tools/smiles2img/sample_output.xlsx
+++ b/tools/smiles2img/sample_output.xlsx
@@ -597,6 +597,11 @@
           <t>鎮痛剤</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CC(=O)Oc1ccccc1C(=O)O</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -619,6 +624,11 @@
           <t>興奮剤</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cn1cnc2c1c(=O)n(C)c(=O)n2C</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -641,6 +651,11 @@
           <t>鎮痛剤</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)O</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -663,6 +678,11 @@
           <t>解熱剤</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CC(=O)Nc1ccc(O)cc1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -683,6 +703,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>溶媒</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CCO</t>
         </is>
       </c>
     </row>
